--- a/salidas/empresas/KHC.xlsx
+++ b/salidas/empresas/KHC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B2" t="n">
-        <v>47.93357086181641</v>
+        <v>47.93357467651367</v>
       </c>
       <c r="C2" t="n">
         <v>79.47000122070312</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B3" t="n">
-        <v>43.82600784301758</v>
+        <v>43.82601165771484</v>
       </c>
       <c r="C3" t="n">
         <v>72.66000366210938</v>
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B4" t="n">
@@ -551,11 +563,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B5" t="n">
-        <v>47.02882766723633</v>
+        <v>47.02881622314453</v>
       </c>
       <c r="C5" t="n">
         <v>77.97000122070312</v>
@@ -576,7 +588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B6" t="n">
@@ -601,11 +613,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B7" t="n">
-        <v>44.60198211669922</v>
+        <v>44.60200500488281</v>
       </c>
       <c r="C7" t="n">
         <v>72.76000213623047</v>
@@ -626,11 +638,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B8" t="n">
-        <v>47.85089111328125</v>
+        <v>47.85089492797852</v>
       </c>
       <c r="C8" t="n">
         <v>78.05999755859375</v>
@@ -651,11 +663,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B9" t="n">
-        <v>47.21338653564453</v>
+        <v>47.2133674621582</v>
       </c>
       <c r="C9" t="n">
         <v>77.01999664306641</v>
@@ -676,11 +688,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B10" t="n">
-        <v>48.51605987548828</v>
+        <v>48.51604843139648</v>
       </c>
       <c r="C10" t="n">
         <v>78.55999755859375</v>
@@ -703,11 +715,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B11" t="n">
-        <v>48.21345901489258</v>
+        <v>48.21344757080078</v>
       </c>
       <c r="C11" t="n">
         <v>78.06999969482422</v>
@@ -730,11 +742,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B12" t="n">
-        <v>51.72856903076172</v>
+        <v>51.72855377197266</v>
       </c>
       <c r="C12" t="n">
         <v>83.19000244140625</v>
@@ -757,11 +769,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B13" t="n">
-        <v>55.01796340942383</v>
+        <v>55.01795196533203</v>
       </c>
       <c r="C13" t="n">
         <v>88.48000335693359</v>
@@ -784,11 +796,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B14" t="n">
-        <v>53.71835327148438</v>
+        <v>53.71836853027344</v>
       </c>
       <c r="C14" t="n">
         <v>86.38999938964844</v>
@@ -811,11 +823,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B15" t="n">
-        <v>56.02165603637695</v>
+        <v>56.02168273925781</v>
       </c>
       <c r="C15" t="n">
         <v>89.48999786376953</v>
@@ -840,11 +852,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B16" t="n">
-        <v>56.03418731689453</v>
+        <v>56.03419876098633</v>
       </c>
       <c r="C16" t="n">
         <v>89.51000213623047</v>
@@ -869,7 +881,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B17" t="n">
@@ -898,11 +910,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B18" t="n">
-        <v>51.48146820068359</v>
+        <v>51.48149108886719</v>
       </c>
       <c r="C18" t="n">
         <v>81.65000152587891</v>
@@ -927,11 +939,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B19" t="n">
-        <v>55.05648422241211</v>
+        <v>55.05648803710938</v>
       </c>
       <c r="C19" t="n">
         <v>87.31999969482422</v>
@@ -956,11 +968,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B20" t="n">
-        <v>56.29860305786133</v>
+        <v>56.29860687255859</v>
       </c>
       <c r="C20" t="n">
         <v>89.29000091552734</v>
@@ -985,11 +997,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B21" t="n">
-        <v>57.69834136962891</v>
+        <v>57.69834518432617</v>
       </c>
       <c r="C21" t="n">
         <v>91.51000213623047</v>
@@ -1014,11 +1026,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B22" t="n">
-        <v>57.63486480712891</v>
+        <v>57.6348762512207</v>
       </c>
       <c r="C22" t="n">
         <v>90.80999755859375</v>
@@ -1043,11 +1055,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B23" t="n">
-        <v>57.36831283569336</v>
+        <v>57.36832427978516</v>
       </c>
       <c r="C23" t="n">
         <v>90.38999938964844</v>
@@ -1072,11 +1084,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B24" t="n">
-        <v>58.91376495361328</v>
+        <v>58.91375350952148</v>
       </c>
       <c r="C24" t="n">
         <v>92.19999694824219</v>
@@ -1101,11 +1113,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B25" t="n">
-        <v>54.72207260131836</v>
+        <v>54.72204208374023</v>
       </c>
       <c r="C25" t="n">
         <v>85.63999938964844</v>
@@ -1130,11 +1142,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B26" t="n">
-        <v>55.885009765625</v>
+        <v>55.88501739501953</v>
       </c>
       <c r="C26" t="n">
         <v>87.45999908447266</v>
@@ -1159,11 +1171,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B27" t="n">
-        <v>51.97195053100586</v>
+        <v>51.97195816040039</v>
       </c>
       <c r="C27" t="n">
         <v>80.75</v>
@@ -1188,11 +1200,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B28" t="n">
-        <v>49.91237258911133</v>
+        <v>49.91236114501953</v>
       </c>
       <c r="C28" t="n">
         <v>77.55000305175781</v>
@@ -1217,11 +1229,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B29" t="n">
-        <v>49.77077865600586</v>
+        <v>49.77077484130859</v>
       </c>
       <c r="C29" t="n">
         <v>77.33000183105469</v>
@@ -1246,11 +1258,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B30" t="n">
-        <v>52.78978729248047</v>
+        <v>52.789794921875</v>
       </c>
       <c r="C30" t="n">
         <v>81.37000274658203</v>
@@ -1275,11 +1287,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B31" t="n">
-        <v>50.4477653503418</v>
+        <v>50.44776153564453</v>
       </c>
       <c r="C31" t="n">
         <v>77.76000213623047</v>
@@ -1304,11 +1316,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B32" t="n">
-        <v>50.85647201538086</v>
+        <v>50.85647964477539</v>
       </c>
       <c r="C32" t="n">
         <v>78.38999938964844</v>
@@ -1333,11 +1345,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B33" t="n">
-        <v>43.49951934814453</v>
+        <v>43.4995231628418</v>
       </c>
       <c r="C33" t="n">
         <v>67.05000305175781</v>
@@ -1362,11 +1374,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B34" t="n">
-        <v>40.78931427001953</v>
+        <v>40.78931045532227</v>
       </c>
       <c r="C34" t="n">
         <v>62.29000091552734</v>
@@ -1391,11 +1403,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B35" t="n">
-        <v>36.91926574707031</v>
+        <v>36.91925811767578</v>
       </c>
       <c r="C35" t="n">
         <v>56.38000106811523</v>
@@ -1420,11 +1432,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B36" t="n">
-        <v>38.04058074951172</v>
+        <v>38.04058456420898</v>
       </c>
       <c r="C36" t="n">
         <v>57.47999954223633</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B37" t="n">
@@ -1478,7 +1490,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B38" t="n">
@@ -1507,11 +1519,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B39" t="n">
-        <v>38.97565841674805</v>
+        <v>38.97565078735352</v>
       </c>
       <c r="C39" t="n">
         <v>58.27000045776367</v>
@@ -1536,11 +1548,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B40" t="n">
-        <v>36.86198806762695</v>
+        <v>36.86199569702148</v>
       </c>
       <c r="C40" t="n">
         <v>55.11000061035156</v>
@@ -1565,11 +1577,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B41" t="n">
-        <v>36.76835250854492</v>
+        <v>36.76834487915039</v>
       </c>
       <c r="C41" t="n">
         <v>54.97000122070312</v>
@@ -1594,11 +1606,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B42" t="n">
-        <v>34.60402297973633</v>
+        <v>34.60401916503906</v>
       </c>
       <c r="C42" t="n">
         <v>51.11999893188477</v>
@@ -1623,11 +1635,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B43" t="n">
-        <v>29.13451957702637</v>
+        <v>29.1345329284668</v>
       </c>
       <c r="C43" t="n">
         <v>43.04000091552734</v>
@@ -1652,11 +1664,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B44" t="n">
-        <v>32.53266143798828</v>
+        <v>32.53265762329102</v>
       </c>
       <c r="C44" t="n">
         <v>48.06000137329102</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B45" t="n">
-        <v>22.46688842773438</v>
+        <v>22.46688461303711</v>
       </c>
       <c r="C45" t="n">
         <v>33.18999862670898</v>
@@ -1710,11 +1722,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B46" t="n">
-        <v>22.37370872497559</v>
+        <v>22.37371063232422</v>
       </c>
       <c r="C46" t="n">
         <v>32.65000152587891</v>
@@ -1739,11 +1751,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B47" t="n">
-        <v>22.77801132202148</v>
+        <v>22.77800750732422</v>
       </c>
       <c r="C47" t="n">
         <v>33.2400016784668</v>
@@ -1768,7 +1780,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B48" t="n">
@@ -1797,11 +1809,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B49" t="n">
-        <v>21.5712947845459</v>
+        <v>21.57129669189453</v>
       </c>
       <c r="C49" t="n">
         <v>31.04000091552734</v>
@@ -1824,11 +1836,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B50" t="n">
-        <v>22.24539756774902</v>
+        <v>22.24539947509766</v>
       </c>
       <c r="C50" t="n">
         <v>32.0099983215332</v>
@@ -1851,11 +1863,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B51" t="n">
-        <v>18.01544952392578</v>
+        <v>18.01545524597168</v>
       </c>
       <c r="C51" t="n">
         <v>25.52000045776367</v>
@@ -1878,11 +1890,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B52" t="n">
-        <v>19.72027969360352</v>
+        <v>19.72027397155762</v>
       </c>
       <c r="C52" t="n">
         <v>27.93499946594238</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B53" t="n">
-        <v>22.82286643981934</v>
+        <v>22.8228645324707</v>
       </c>
       <c r="C53" t="n">
         <v>32.33000183105469</v>
@@ -1932,11 +1944,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B54" t="n">
-        <v>21.79277801513672</v>
+        <v>21.79277992248535</v>
       </c>
       <c r="C54" t="n">
         <v>30.5</v>
@@ -1959,11 +1971,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B55" t="n">
-        <v>22.95743751525879</v>
+        <v>22.95744323730469</v>
       </c>
       <c r="C55" t="n">
         <v>32.13000106811523</v>
@@ -1986,11 +1998,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B56" t="n">
-        <v>20.8639030456543</v>
+        <v>20.86390495300293</v>
       </c>
       <c r="C56" t="n">
         <v>29.20000076293945</v>
@@ -2013,11 +2025,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B57" t="n">
-        <v>17.69859313964844</v>
+        <v>17.69858932495117</v>
       </c>
       <c r="C57" t="n">
         <v>24.77000045776367</v>
@@ -2042,11 +2054,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B58" t="n">
-        <v>17.98114585876465</v>
+        <v>17.98114776611328</v>
       </c>
       <c r="C58" t="n">
         <v>24.73999977111816</v>
@@ -2071,11 +2083,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B59" t="n">
-        <v>22.04398727416992</v>
+        <v>22.04399108886719</v>
       </c>
       <c r="C59" t="n">
         <v>30.32999992370605</v>
@@ -2100,11 +2112,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B60" t="n">
-        <v>22.43494606018066</v>
+        <v>22.4349479675293</v>
       </c>
       <c r="C60" t="n">
         <v>30.46999931335449</v>
@@ -2129,11 +2141,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B61" t="n">
-        <v>23.48048782348633</v>
+        <v>23.48048210144043</v>
       </c>
       <c r="C61" t="n">
         <v>31.88999938964844</v>
@@ -2158,11 +2170,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B62" t="n">
-        <v>25.3138599395752</v>
+        <v>25.31385803222656</v>
       </c>
       <c r="C62" t="n">
         <v>34.38000106811523</v>
@@ -2185,11 +2197,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B63" t="n">
-        <v>26.09543418884277</v>
+        <v>26.09543991088867</v>
       </c>
       <c r="C63" t="n">
         <v>35.04000091552734</v>
@@ -2212,7 +2224,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B64" t="n">
@@ -2239,11 +2251,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B65" t="n">
-        <v>22.78137016296387</v>
+        <v>22.78137588500977</v>
       </c>
       <c r="C65" t="n">
         <v>30.59000015258789</v>
@@ -2266,11 +2278,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B66" t="n">
-        <v>24.82502174377441</v>
+        <v>24.82502365112305</v>
       </c>
       <c r="C66" t="n">
         <v>32.93999862670898</v>
@@ -2293,11 +2305,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B67" t="n">
-        <v>26.12129020690918</v>
+        <v>26.12128829956055</v>
       </c>
       <c r="C67" t="n">
         <v>34.65999984741211</v>
@@ -2320,11 +2332,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B68" t="n">
-        <v>25.25459098815918</v>
+        <v>25.25459671020508</v>
       </c>
       <c r="C68" t="n">
         <v>33.5099983215332</v>
@@ -2347,11 +2359,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B69" t="n">
-        <v>27.41754913330078</v>
+        <v>27.41755294799805</v>
       </c>
       <c r="C69" t="n">
         <v>36.38000106811523</v>
@@ -2376,11 +2388,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B70" t="n">
-        <v>30.45406532287598</v>
+        <v>30.45407104492188</v>
       </c>
       <c r="C70" t="n">
         <v>40</v>
@@ -2405,11 +2417,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B71" t="n">
-        <v>31.43620300292969</v>
+        <v>31.43619918823242</v>
       </c>
       <c r="C71" t="n">
         <v>41.29000091552734</v>
@@ -2434,11 +2446,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B72" t="n">
-        <v>33.49053573608398</v>
+        <v>33.49053955078125</v>
       </c>
       <c r="C72" t="n">
         <v>43.59000015258789</v>
@@ -2463,7 +2475,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B73" t="n">
@@ -2492,11 +2504,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B74" t="n">
-        <v>29.55680084228516</v>
+        <v>29.55679512023926</v>
       </c>
       <c r="C74" t="n">
         <v>38.47000122070312</v>
@@ -2521,11 +2533,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B75" t="n">
-        <v>27.9610424041748</v>
+        <v>27.96104049682617</v>
       </c>
       <c r="C75" t="n">
         <v>35.9900016784668</v>
@@ -2550,11 +2562,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B76" t="n">
-        <v>28.60588073730469</v>
+        <v>28.60587310791016</v>
       </c>
       <c r="C76" t="n">
         <v>36.81999969482422</v>
@@ -2579,11 +2591,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B77" t="n">
-        <v>27.88335037231445</v>
+        <v>27.88335418701172</v>
       </c>
       <c r="C77" t="n">
         <v>35.88999938964844</v>
@@ -2608,11 +2620,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B78" t="n">
-        <v>26.4068775177002</v>
+        <v>26.40687561035156</v>
       </c>
       <c r="C78" t="n">
         <v>33.61000061035156</v>
@@ -2637,7 +2649,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B79" t="n">
@@ -2666,11 +2678,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B80" t="n">
-        <v>28.12753105163574</v>
+        <v>28.12752914428711</v>
       </c>
       <c r="C80" t="n">
         <v>35.79999923706055</v>
@@ -2695,11 +2707,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B81" t="n">
-        <v>30.8145694732666</v>
+        <v>30.81457138061523</v>
       </c>
       <c r="C81" t="n">
         <v>39.22000122070312</v>
@@ -2724,7 +2736,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B82" t="n">
@@ -2753,7 +2765,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B83" t="n">
@@ -2782,11 +2794,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B84" t="n">
-        <v>30.34148597717285</v>
+        <v>30.34148788452148</v>
       </c>
       <c r="C84" t="n">
         <v>37.83000183105469</v>
@@ -2811,11 +2823,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B85" t="n">
-        <v>30.59012222290039</v>
+        <v>30.59011268615723</v>
       </c>
       <c r="C85" t="n">
         <v>38.13999938964844</v>
@@ -2840,11 +2852,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B86" t="n">
-        <v>29.53943824768066</v>
+        <v>29.5394344329834</v>
       </c>
       <c r="C86" t="n">
         <v>36.83000183105469</v>
@@ -2869,11 +2881,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B87" t="n">
-        <v>30.30817794799805</v>
+        <v>30.30817413330078</v>
       </c>
       <c r="C87" t="n">
         <v>37.40000152587891</v>
@@ -2898,7 +2910,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B88" t="n">
@@ -2927,11 +2939,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B89" t="n">
-        <v>31.17528343200684</v>
+        <v>31.1752815246582</v>
       </c>
       <c r="C89" t="n">
         <v>38.47000122070312</v>
@@ -2956,11 +2968,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B90" t="n">
-        <v>32.21921157836914</v>
+        <v>32.21920394897461</v>
       </c>
       <c r="C90" t="n">
         <v>39.34999847412109</v>
@@ -2985,11 +2997,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B91" t="n">
-        <v>33.33275604248047</v>
+        <v>33.33275985717773</v>
       </c>
       <c r="C91" t="n">
         <v>40.70999908447266</v>
@@ -3014,11 +3026,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B92" t="n">
-        <v>33.18537902832031</v>
+        <v>33.18537521362305</v>
       </c>
       <c r="C92" t="n">
         <v>40.52999877929688</v>
@@ -3043,11 +3055,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B93" t="n">
-        <v>31.88350677490234</v>
+        <v>31.88349914550781</v>
       </c>
       <c r="C93" t="n">
         <v>38.93999862670898</v>
@@ -3072,11 +3084,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B94" t="n">
-        <v>31.99641990661621</v>
+        <v>31.99642372131348</v>
       </c>
       <c r="C94" t="n">
         <v>38.66999816894531</v>
@@ -3101,11 +3113,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B95" t="n">
-        <v>32.49287796020508</v>
+        <v>32.49288177490234</v>
       </c>
       <c r="C95" t="n">
         <v>39.27000045776367</v>
@@ -3130,11 +3142,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B96" t="n">
-        <v>31.62409019470215</v>
+        <v>31.62408638000488</v>
       </c>
       <c r="C96" t="n">
         <v>38.22000122070312</v>
@@ -3159,11 +3171,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B97" t="n">
-        <v>29.68179893493652</v>
+        <v>29.68179512023926</v>
       </c>
       <c r="C97" t="n">
         <v>35.5</v>
@@ -3188,11 +3200,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B98" t="n">
-        <v>30.25035285949707</v>
+        <v>30.25035667419434</v>
       </c>
       <c r="C98" t="n">
         <v>36.18000030517578</v>
@@ -3217,7 +3229,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B99" t="n">
@@ -3246,11 +3258,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B100" t="n">
-        <v>28.46479988098145</v>
+        <v>28.46480178833008</v>
       </c>
       <c r="C100" t="n">
         <v>33.63999938964844</v>
@@ -3275,7 +3287,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B101" t="n">
@@ -3304,11 +3316,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B102" t="n">
-        <v>30.05131530761719</v>
+        <v>30.05131721496582</v>
       </c>
       <c r="C102" t="n">
         <v>35.11000061035156</v>
@@ -3333,7 +3345,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B103" t="n">
@@ -3362,7 +3374,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B104" t="n">
@@ -3391,11 +3403,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B105" t="n">
-        <v>30.19682121276855</v>
+        <v>30.19682312011719</v>
       </c>
       <c r="C105" t="n">
         <v>35.27999877929688</v>
@@ -3420,11 +3432,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B106" t="n">
-        <v>31.94487953186035</v>
+        <v>31.94489097595215</v>
       </c>
       <c r="C106" t="n">
         <v>36.90000152587891</v>
@@ -3449,11 +3461,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B107" t="n">
-        <v>33.42525863647461</v>
+        <v>33.42525482177734</v>
       </c>
       <c r="C107" t="n">
         <v>38.61000061035156</v>
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B108" t="n">
@@ -3507,11 +3519,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B109" t="n">
-        <v>28.21891212463379</v>
+        <v>28.21891021728516</v>
       </c>
       <c r="C109" t="n">
         <v>32.22000122070312</v>
@@ -3536,11 +3548,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B110" t="n">
-        <v>30.83760452270508</v>
+        <v>30.83760833740234</v>
       </c>
       <c r="C110" t="n">
         <v>35.20999908447266</v>
@@ -3565,11 +3577,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B111" t="n">
-        <v>31.38634300231934</v>
+        <v>31.38634872436523</v>
       </c>
       <c r="C111" t="n">
         <v>35.43000030517578</v>
@@ -3594,11 +3606,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B112" t="n">
-        <v>31.10286903381348</v>
+        <v>31.10287094116211</v>
       </c>
       <c r="C112" t="n">
         <v>35.11000061035156</v>
@@ -3623,11 +3635,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B113" t="n">
-        <v>29.64118576049805</v>
+        <v>29.64118385314941</v>
       </c>
       <c r="C113" t="n">
         <v>33.45999908447266</v>
@@ -3652,11 +3664,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B114" t="n">
-        <v>28.68053245544434</v>
+        <v>28.68053436279297</v>
       </c>
       <c r="C114" t="n">
         <v>31.96999931335449</v>
@@ -3681,11 +3693,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B115" t="n">
-        <v>27.55017471313477</v>
+        <v>27.5501766204834</v>
       </c>
       <c r="C115" t="n">
         <v>30.70999908447266</v>
@@ -3710,11 +3722,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B116" t="n">
-        <v>26.76969337463379</v>
+        <v>26.76969146728516</v>
       </c>
       <c r="C116" t="n">
         <v>29.84000015258789</v>
@@ -3739,11 +3751,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B117" t="n">
-        <v>27.55017471313477</v>
+        <v>27.5501766204834</v>
       </c>
       <c r="C117" t="n">
         <v>30.70999908447266</v>
@@ -3768,11 +3780,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B118" t="n">
-        <v>27.6525993347168</v>
+        <v>27.65260124206543</v>
       </c>
       <c r="C118" t="n">
         <v>30.43000030517578</v>
@@ -3797,11 +3809,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B119" t="n">
-        <v>26.44399261474609</v>
+        <v>26.44399070739746</v>
       </c>
       <c r="C119" t="n">
         <v>29.10000038146973</v>
@@ -3826,7 +3838,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B120" t="n">
@@ -3855,11 +3867,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B121" t="n">
-        <v>23.8159294128418</v>
+        <v>23.81592750549316</v>
       </c>
       <c r="C121" t="n">
         <v>25.81999969482422</v>
@@ -3884,7 +3896,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B122" t="n">
@@ -3911,11 +3923,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B123" t="n">
-        <v>26.17789268493652</v>
+        <v>26.17789077758789</v>
       </c>
       <c r="C123" t="n">
         <v>27.96999931335449</v>
@@ -3938,7 +3950,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B124" t="n">
@@ -3965,11 +3977,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B125" t="n">
-        <v>23.14548873901367</v>
+        <v>23.14548683166504</v>
       </c>
       <c r="C125" t="n">
         <v>24.72999954223633</v>
@@ -3992,7 +4004,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B126" t="n">
@@ -4019,7 +4031,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B127" t="n">
@@ -4046,7 +4058,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B128" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B129" t="n">
@@ -4100,7 +4112,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B130" t="n">
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B131" t="n">
@@ -4154,7 +4166,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B132" t="n">
@@ -4181,7 +4193,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B133" t="n">
@@ -4208,7 +4220,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B134" t="n">
@@ -4235,7 +4247,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B135" t="n">
@@ -4262,17 +4274,17 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B136" t="n">
-        <v>23.79000091552734</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="C136" t="n">
-        <v>23.79000091552734</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="D136" t="n">
-        <v>402273800</v>
+        <v>415736700</v>
       </c>
       <c r="E136" t="n">
         <v>-2.85</v>
@@ -4282,10 +4294,10 @@
         <v>1185823758</v>
       </c>
       <c r="H136" t="n">
-        <v>28210748288.47408</v>
+        <v>28293755589.64938</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3392357399538625</v>
+        <v>0.3505889447696493</v>
       </c>
     </row>
   </sheetData>
@@ -4317,75 +4329,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41638</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -4421,13 +4433,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -4463,13 +4475,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -4505,13 +4517,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -4538,7 +4550,7 @@
       <c r="I5" t="n">
         <v>-0.16</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="K5" t="n">
@@ -4551,13 +4563,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42002</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -4584,7 +4596,7 @@
       <c r="I6" t="n">
         <v>0.03999999999999998</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="K6" t="n">
@@ -4597,13 +4609,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42093</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4630,7 +4642,7 @@
       <c r="I7" t="n">
         <v>-0.73</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="K7" t="n">
@@ -4643,13 +4655,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42184</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4676,7 +4688,7 @@
       <c r="I8" t="n">
         <v>-0.9800000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="K8" t="n">
@@ -4689,13 +4701,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42275</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42372</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4722,7 +4734,7 @@
       <c r="I9" t="n">
         <v>-0.7100000000000002</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="K9" t="n">
@@ -4735,13 +4747,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42373</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -4768,7 +4780,7 @@
       <c r="I10" t="n">
         <v>-0.2200000000000002</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K10" t="n">
@@ -4781,13 +4793,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42464</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42554</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -4814,7 +4826,7 @@
       <c r="I11" t="n">
         <v>1.32</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K11" t="n">
@@ -4827,13 +4839,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42555</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -4860,7 +4872,7 @@
       <c r="I12" t="n">
         <v>2.28</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K12" t="n">
@@ -4873,13 +4885,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42646</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -4906,7 +4918,7 @@
       <c r="I13" t="n">
         <v>2.82</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K13" t="n">
@@ -4919,13 +4931,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -4952,7 +4964,7 @@
       <c r="I14" t="n">
         <v>2.82</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K14" t="n">
@@ -4965,13 +4977,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -4998,7 +5010,7 @@
       <c r="I15" t="n">
         <v>3.13</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K15" t="n">
@@ -5011,13 +5023,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -5044,7 +5056,7 @@
       <c r="I16" t="n">
         <v>3.21</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K16" t="n">
@@ -5057,13 +5069,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43099</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -5090,7 +5102,7 @@
       <c r="I17" t="n">
         <v>8.959999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K17" t="n">
@@ -5103,13 +5115,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -5136,7 +5148,7 @@
       <c r="I18" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K18" t="n">
@@ -5149,13 +5161,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -5182,7 +5194,7 @@
       <c r="I19" t="n">
         <v>8.719999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K19" t="n">
@@ -5195,13 +5207,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -5228,7 +5240,7 @@
       <c r="I20" t="n">
         <v>8.459999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K20" t="n">
@@ -5241,13 +5253,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43463</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -5274,7 +5286,7 @@
       <c r="I21" t="n">
         <v>-8.360000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="K21" t="n">
@@ -5287,13 +5299,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>43690</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -5320,7 +5332,7 @@
       <c r="I22" t="n">
         <v>-8.840000000000002</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>43690</v>
       </c>
       <c r="K22" t="n">
@@ -5333,13 +5345,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>43690</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -5366,7 +5378,7 @@
       <c r="I23" t="n">
         <v>-9.090000000000002</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>43690</v>
       </c>
       <c r="K23" t="n">
@@ -5379,13 +5391,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -5412,7 +5424,7 @@
       <c r="I24" t="n">
         <v>-8.860000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K24" t="n">
@@ -5425,13 +5437,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43827</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -5458,7 +5470,7 @@
       <c r="I25" t="n">
         <v>1.59</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K25" t="n">
@@ -5471,13 +5483,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43918</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -5504,7 +5516,7 @@
       <c r="I26" t="n">
         <v>1.57</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K26" t="n">
@@ -5517,13 +5529,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>44009</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -5550,7 +5562,7 @@
       <c r="I27" t="n">
         <v>-0.1500000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K27" t="n">
@@ -5563,13 +5575,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44100</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -5596,7 +5608,7 @@
       <c r="I28" t="n">
         <v>-0.4000000000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K28" t="n">
@@ -5609,13 +5621,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44191</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -5642,7 +5654,7 @@
       <c r="I29" t="n">
         <v>0.2899999999999998</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="K29" t="n">
@@ -5655,13 +5667,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44282</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -5688,7 +5700,7 @@
       <c r="I30" t="n">
         <v>0.4399999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K30" t="n">
@@ -5701,13 +5713,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44373</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -5734,7 +5746,7 @@
       <c r="I31" t="n">
         <v>1.77</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K31" t="n">
@@ -5747,13 +5759,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44374</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44464</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -5780,7 +5792,7 @@
       <c r="I32" t="n">
         <v>1.87</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K32" t="n">
@@ -5793,13 +5805,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44465</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44555</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -5826,7 +5838,7 @@
       <c r="I33" t="n">
         <v>0.8200000000000001</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K33" t="n">
@@ -5839,13 +5851,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44556</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44646</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -5872,7 +5884,7 @@
       <c r="I34" t="n">
         <v>0.99</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K34" t="n">
@@ -5885,13 +5897,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44647</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44737</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -5918,7 +5930,7 @@
       <c r="I35" t="n">
         <v>1.22</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K35" t="n">
@@ -5931,13 +5943,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44738</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44828</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -5964,7 +5976,7 @@
       <c r="I36" t="n">
         <v>0.9799999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K36" t="n">
@@ -5977,13 +5989,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44829</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -6010,7 +6022,7 @@
       <c r="I37" t="n">
         <v>1.91</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="K37" t="n">
@@ -6023,13 +6035,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -6056,7 +6068,7 @@
       <c r="I38" t="n">
         <v>1.96</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K38" t="n">
@@ -6069,13 +6081,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -6102,7 +6114,7 @@
       <c r="I39" t="n">
         <v>2.56</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K39" t="n">
@@ -6115,13 +6127,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -6148,7 +6160,7 @@
       <c r="I40" t="n">
         <v>2.42</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K40" t="n">
@@ -6161,13 +6173,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -6194,7 +6206,7 @@
       <c r="I41" t="n">
         <v>2.31</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K41" t="n">
@@ -6207,13 +6219,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -6240,7 +6252,7 @@
       <c r="I42" t="n">
         <v>2.29</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K42" t="n">
@@ -6253,13 +6265,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -6286,7 +6298,7 @@
       <c r="I43" t="n">
         <v>1.56</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K43" t="n">
@@ -6299,13 +6311,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -6332,7 +6344,7 @@
       <c r="I44" t="n">
         <v>1.11</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K44" t="n">
@@ -6345,13 +6357,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -6378,7 +6390,7 @@
       <c r="I45" t="n">
         <v>2.26</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K45" t="n">
@@ -6391,13 +6403,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -6424,7 +6436,7 @@
       <c r="I46" t="n">
         <v>2.19</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K46" t="n">
@@ -6437,13 +6449,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -6470,7 +6482,7 @@
       <c r="I47" t="n">
         <v>-4.49</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="K47" t="n">
@@ -6483,13 +6495,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -6516,7 +6528,7 @@
       <c r="I48" t="n">
         <v>-3.73</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="K48" t="n">
@@ -6529,13 +6541,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>46018</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -6562,7 +6574,7 @@
       <c r="I49" t="n">
         <v>-4.93</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K49" t="n">
@@ -6575,13 +6587,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -6608,7 +6620,7 @@
       <c r="I50" t="n">
         <v>-4.85</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K50" t="n">
@@ -6621,13 +6633,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>46200</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -6654,7 +6666,7 @@
       <c r="I51" t="n">
         <v>-2.85</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K51" t="n">
@@ -6691,52 +6703,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42218</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>42226</v>
       </c>
       <c r="C2" t="n">
@@ -6765,10 +6777,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C3" t="n">
@@ -6797,10 +6809,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42428</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="C4" t="n">
@@ -6829,10 +6841,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C5" t="n">
@@ -6861,10 +6873,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C6" t="n">
@@ -6893,10 +6905,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42673</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C7" t="n">
@@ -6925,10 +6937,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42784</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C8" t="n">
@@ -6957,10 +6969,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42854</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C9" t="n">
@@ -6989,10 +7001,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42945</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C10" t="n">
@@ -7021,10 +7033,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43036</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C11" t="n">
@@ -7053,10 +7065,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43141</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C12" t="n">
@@ -7085,10 +7097,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43218</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C13" t="n">
@@ -7117,10 +7129,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43309</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C14" t="n">
@@ -7149,10 +7161,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43400</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C15" t="n">
@@ -7181,10 +7193,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43621</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="C16" t="n">
@@ -7213,10 +7225,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43680</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43690</v>
       </c>
       <c r="C17" t="n">
@@ -7245,10 +7257,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43764</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C18" t="n">
@@ -7277,10 +7289,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43869</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C19" t="n">
@@ -7309,10 +7321,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43946</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C20" t="n">
@@ -7341,10 +7353,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44037</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C21" t="n">
@@ -7373,10 +7385,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44128</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C22" t="n">
@@ -7405,10 +7417,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44240</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="C23" t="n">
@@ -7437,10 +7449,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44310</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C24" t="n">
@@ -7469,10 +7481,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C25" t="n">
@@ -7501,10 +7513,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44492</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C26" t="n">
@@ -7533,10 +7545,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44604</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="C27" t="n">
@@ -7565,10 +7577,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44674</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C28" t="n">
@@ -7597,10 +7609,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44765</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C29" t="n">
@@ -7629,10 +7641,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44856</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C30" t="n">
@@ -7661,10 +7673,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44968</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="C31" t="n">
@@ -7693,10 +7705,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45045</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C32" t="n">
@@ -7725,10 +7737,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45136</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C33" t="n">
@@ -7757,10 +7769,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45227</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C34" t="n">
@@ -7789,10 +7801,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45332</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C35" t="n">
@@ -7821,10 +7833,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45409</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C36" t="n">
@@ -7853,10 +7865,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45500</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C37" t="n">
@@ -7885,10 +7897,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45591</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C38" t="n">
@@ -7917,10 +7929,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45696</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C39" t="n">
@@ -7949,10 +7961,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45773</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C40" t="n">
@@ -7981,10 +7993,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45864</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="C41" t="n">
@@ -8013,10 +8025,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45955</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C42" t="n">
@@ -8045,10 +8057,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C43" t="n">
@@ -8077,10 +8089,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C44" t="n">
@@ -8109,10 +8121,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46235</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C45" t="n">
@@ -8159,12 +8171,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/KHC.xlsx
+++ b/salidas/empresas/KHC.xlsx
@@ -498,7 +498,7 @@
         <v>42216</v>
       </c>
       <c r="B2" t="n">
-        <v>47.93357467651367</v>
+        <v>47.9335823059082</v>
       </c>
       <c r="C2" t="n">
         <v>79.47000122070312</v>
@@ -517,7 +517,7 @@
         <v>42247</v>
       </c>
       <c r="B3" t="n">
-        <v>43.82601165771484</v>
+        <v>43.82602310180664</v>
       </c>
       <c r="C3" t="n">
         <v>72.66000366210938</v>
@@ -542,7 +542,7 @@
         <v>42277</v>
       </c>
       <c r="B4" t="n">
-        <v>42.57143402099609</v>
+        <v>42.57143783569336</v>
       </c>
       <c r="C4" t="n">
         <v>70.58000183105469</v>
@@ -592,7 +592,7 @@
         <v>42338</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80455017089844</v>
+        <v>44.80454254150391</v>
       </c>
       <c r="C6" t="n">
         <v>73.69000244140625</v>
@@ -617,7 +617,7 @@
         <v>42369</v>
       </c>
       <c r="B7" t="n">
-        <v>44.60200500488281</v>
+        <v>44.60199356079102</v>
       </c>
       <c r="C7" t="n">
         <v>72.76000213623047</v>
@@ -642,7 +642,7 @@
         <v>42400</v>
       </c>
       <c r="B8" t="n">
-        <v>47.85089492797852</v>
+        <v>47.85091018676758</v>
       </c>
       <c r="C8" t="n">
         <v>78.05999755859375</v>
@@ -667,7 +667,7 @@
         <v>42429</v>
       </c>
       <c r="B9" t="n">
-        <v>47.2133674621582</v>
+        <v>47.2133903503418</v>
       </c>
       <c r="C9" t="n">
         <v>77.01999664306641</v>
@@ -692,7 +692,7 @@
         <v>42460</v>
       </c>
       <c r="B10" t="n">
-        <v>48.51604843139648</v>
+        <v>48.51605224609375</v>
       </c>
       <c r="C10" t="n">
         <v>78.55999755859375</v>
@@ -719,7 +719,7 @@
         <v>42490</v>
       </c>
       <c r="B11" t="n">
-        <v>48.21344757080078</v>
+        <v>48.21345520019531</v>
       </c>
       <c r="C11" t="n">
         <v>78.06999969482422</v>
@@ -746,7 +746,7 @@
         <v>42521</v>
       </c>
       <c r="B12" t="n">
-        <v>51.72855377197266</v>
+        <v>51.72856903076172</v>
       </c>
       <c r="C12" t="n">
         <v>83.19000244140625</v>
@@ -773,7 +773,7 @@
         <v>42551</v>
       </c>
       <c r="B13" t="n">
-        <v>55.01795196533203</v>
+        <v>55.01794815063477</v>
       </c>
       <c r="C13" t="n">
         <v>88.48000335693359</v>
@@ -800,7 +800,7 @@
         <v>42582</v>
       </c>
       <c r="B14" t="n">
-        <v>53.71836853027344</v>
+        <v>53.71836471557617</v>
       </c>
       <c r="C14" t="n">
         <v>86.38999938964844</v>
@@ -827,7 +827,7 @@
         <v>42613</v>
       </c>
       <c r="B15" t="n">
-        <v>56.02168273925781</v>
+        <v>56.02167510986328</v>
       </c>
       <c r="C15" t="n">
         <v>89.48999786376953</v>
@@ -856,7 +856,7 @@
         <v>42643</v>
       </c>
       <c r="B16" t="n">
-        <v>56.03419876098633</v>
+        <v>56.03419494628906</v>
       </c>
       <c r="C16" t="n">
         <v>89.51000213623047</v>
@@ -885,7 +885,7 @@
         <v>42674</v>
       </c>
       <c r="B17" t="n">
-        <v>55.68362808227539</v>
+        <v>55.68362045288086</v>
       </c>
       <c r="C17" t="n">
         <v>88.94999694824219</v>
@@ -914,7 +914,7 @@
         <v>42704</v>
       </c>
       <c r="B18" t="n">
-        <v>51.48149108886719</v>
+        <v>51.48147201538086</v>
       </c>
       <c r="C18" t="n">
         <v>81.65000152587891</v>
@@ -943,7 +943,7 @@
         <v>42735</v>
       </c>
       <c r="B19" t="n">
-        <v>55.05648803710938</v>
+        <v>55.05649948120117</v>
       </c>
       <c r="C19" t="n">
         <v>87.31999969482422</v>
@@ -972,7 +972,7 @@
         <v>42766</v>
       </c>
       <c r="B20" t="n">
-        <v>56.29860687255859</v>
+        <v>56.29861068725586</v>
       </c>
       <c r="C20" t="n">
         <v>89.29000091552734</v>
@@ -1001,7 +1001,7 @@
         <v>42794</v>
       </c>
       <c r="B21" t="n">
-        <v>57.69834518432617</v>
+        <v>57.69834899902344</v>
       </c>
       <c r="C21" t="n">
         <v>91.51000213623047</v>
@@ -1059,7 +1059,7 @@
         <v>42855</v>
       </c>
       <c r="B23" t="n">
-        <v>57.36832427978516</v>
+        <v>57.36832046508789</v>
       </c>
       <c r="C23" t="n">
         <v>90.38999938964844</v>
@@ -1088,7 +1088,7 @@
         <v>42886</v>
       </c>
       <c r="B24" t="n">
-        <v>58.91375350952148</v>
+        <v>58.91375732421875</v>
       </c>
       <c r="C24" t="n">
         <v>92.19999694824219</v>
@@ -1117,7 +1117,7 @@
         <v>42916</v>
       </c>
       <c r="B25" t="n">
-        <v>54.72204208374023</v>
+        <v>54.72206115722656</v>
       </c>
       <c r="C25" t="n">
         <v>85.63999938964844</v>
@@ -1146,7 +1146,7 @@
         <v>42947</v>
       </c>
       <c r="B26" t="n">
-        <v>55.88501739501953</v>
+        <v>55.88500213623047</v>
       </c>
       <c r="C26" t="n">
         <v>87.45999908447266</v>
@@ -1175,7 +1175,7 @@
         <v>42978</v>
       </c>
       <c r="B27" t="n">
-        <v>51.97195816040039</v>
+        <v>51.97193908691406</v>
       </c>
       <c r="C27" t="n">
         <v>80.75</v>
@@ -1204,7 +1204,7 @@
         <v>43008</v>
       </c>
       <c r="B28" t="n">
-        <v>49.91236114501953</v>
+        <v>49.91237640380859</v>
       </c>
       <c r="C28" t="n">
         <v>77.55000305175781</v>
@@ -1233,7 +1233,7 @@
         <v>43039</v>
       </c>
       <c r="B29" t="n">
-        <v>49.77077484130859</v>
+        <v>49.77077102661133</v>
       </c>
       <c r="C29" t="n">
         <v>77.33000183105469</v>
@@ -1262,7 +1262,7 @@
         <v>43069</v>
       </c>
       <c r="B30" t="n">
-        <v>52.789794921875</v>
+        <v>52.78980255126953</v>
       </c>
       <c r="C30" t="n">
         <v>81.37000274658203</v>
@@ -1291,7 +1291,7 @@
         <v>43100</v>
       </c>
       <c r="B31" t="n">
-        <v>50.44776153564453</v>
+        <v>50.44775772094727</v>
       </c>
       <c r="C31" t="n">
         <v>77.76000213623047</v>
@@ -1349,7 +1349,7 @@
         <v>43159</v>
       </c>
       <c r="B33" t="n">
-        <v>43.4995231628418</v>
+        <v>43.49951171875</v>
       </c>
       <c r="C33" t="n">
         <v>67.05000305175781</v>
@@ -1378,7 +1378,7 @@
         <v>43190</v>
       </c>
       <c r="B34" t="n">
-        <v>40.78931045532227</v>
+        <v>40.789306640625</v>
       </c>
       <c r="C34" t="n">
         <v>62.29000091552734</v>
@@ -1407,7 +1407,7 @@
         <v>43220</v>
       </c>
       <c r="B35" t="n">
-        <v>36.91925811767578</v>
+        <v>36.91927719116211</v>
       </c>
       <c r="C35" t="n">
         <v>56.38000106811523</v>
@@ -1436,7 +1436,7 @@
         <v>43251</v>
       </c>
       <c r="B36" t="n">
-        <v>38.04058456420898</v>
+        <v>38.04057693481445</v>
       </c>
       <c r="C36" t="n">
         <v>57.47999954223633</v>
@@ -1465,7 +1465,7 @@
         <v>43281</v>
       </c>
       <c r="B37" t="n">
-        <v>41.57461547851562</v>
+        <v>41.57462692260742</v>
       </c>
       <c r="C37" t="n">
         <v>62.81999969482422</v>
@@ -1523,7 +1523,7 @@
         <v>43343</v>
       </c>
       <c r="B39" t="n">
-        <v>38.97565078735352</v>
+        <v>38.97565460205078</v>
       </c>
       <c r="C39" t="n">
         <v>58.27000045776367</v>
@@ -1581,7 +1581,7 @@
         <v>43404</v>
       </c>
       <c r="B41" t="n">
-        <v>36.76834487915039</v>
+        <v>36.76835250854492</v>
       </c>
       <c r="C41" t="n">
         <v>54.97000122070312</v>
@@ -1610,7 +1610,7 @@
         <v>43434</v>
       </c>
       <c r="B42" t="n">
-        <v>34.60401916503906</v>
+        <v>34.6040153503418</v>
       </c>
       <c r="C42" t="n">
         <v>51.11999893188477</v>
@@ -1668,7 +1668,7 @@
         <v>43496</v>
       </c>
       <c r="B44" t="n">
-        <v>32.53265762329102</v>
+        <v>32.53265380859375</v>
       </c>
       <c r="C44" t="n">
         <v>48.06000137329102</v>
@@ -1697,7 +1697,7 @@
         <v>43524</v>
       </c>
       <c r="B45" t="n">
-        <v>22.46688461303711</v>
+        <v>22.46689414978027</v>
       </c>
       <c r="C45" t="n">
         <v>33.18999862670898</v>
@@ -1726,7 +1726,7 @@
         <v>43555</v>
       </c>
       <c r="B46" t="n">
-        <v>22.37371063232422</v>
+        <v>22.37370872497559</v>
       </c>
       <c r="C46" t="n">
         <v>32.65000152587891</v>
@@ -1755,7 +1755,7 @@
         <v>43585</v>
       </c>
       <c r="B47" t="n">
-        <v>22.77800750732422</v>
+        <v>22.77800941467285</v>
       </c>
       <c r="C47" t="n">
         <v>33.2400016784668</v>
@@ -1784,7 +1784,7 @@
         <v>43616</v>
       </c>
       <c r="B48" t="n">
-        <v>19.21541023254395</v>
+        <v>19.21540451049805</v>
       </c>
       <c r="C48" t="n">
         <v>27.64999961853027</v>
@@ -1813,7 +1813,7 @@
         <v>43646</v>
       </c>
       <c r="B49" t="n">
-        <v>21.57129669189453</v>
+        <v>21.5712947845459</v>
       </c>
       <c r="C49" t="n">
         <v>31.04000091552734</v>
@@ -1840,7 +1840,7 @@
         <v>43677</v>
       </c>
       <c r="B50" t="n">
-        <v>22.24539947509766</v>
+        <v>22.24539566040039</v>
       </c>
       <c r="C50" t="n">
         <v>32.0099983215332</v>
@@ -1867,7 +1867,7 @@
         <v>43708</v>
       </c>
       <c r="B51" t="n">
-        <v>18.01545524597168</v>
+        <v>18.01545143127441</v>
       </c>
       <c r="C51" t="n">
         <v>25.52000045776367</v>
@@ -1894,7 +1894,7 @@
         <v>43738</v>
       </c>
       <c r="B52" t="n">
-        <v>19.72027397155762</v>
+        <v>19.72028350830078</v>
       </c>
       <c r="C52" t="n">
         <v>27.93499946594238</v>
@@ -1921,7 +1921,7 @@
         <v>43769</v>
       </c>
       <c r="B53" t="n">
-        <v>22.8228645324707</v>
+        <v>22.82286643981934</v>
       </c>
       <c r="C53" t="n">
         <v>32.33000183105469</v>
@@ -1948,7 +1948,7 @@
         <v>43799</v>
       </c>
       <c r="B54" t="n">
-        <v>21.79277992248535</v>
+        <v>21.79278182983398</v>
       </c>
       <c r="C54" t="n">
         <v>30.5</v>
@@ -2002,7 +2002,7 @@
         <v>43861</v>
       </c>
       <c r="B56" t="n">
-        <v>20.86390495300293</v>
+        <v>20.86390113830566</v>
       </c>
       <c r="C56" t="n">
         <v>29.20000076293945</v>
@@ -2058,7 +2058,7 @@
         <v>43921</v>
       </c>
       <c r="B58" t="n">
-        <v>17.98114776611328</v>
+        <v>17.98114585876465</v>
       </c>
       <c r="C58" t="n">
         <v>24.73999977111816</v>
@@ -2087,7 +2087,7 @@
         <v>43951</v>
       </c>
       <c r="B59" t="n">
-        <v>22.04399108886719</v>
+        <v>22.04398918151855</v>
       </c>
       <c r="C59" t="n">
         <v>30.32999992370605</v>
@@ -2174,7 +2174,7 @@
         <v>44043</v>
       </c>
       <c r="B62" t="n">
-        <v>25.31385803222656</v>
+        <v>25.31386184692383</v>
       </c>
       <c r="C62" t="n">
         <v>34.38000106811523</v>
@@ -2201,7 +2201,7 @@
         <v>44074</v>
       </c>
       <c r="B63" t="n">
-        <v>26.09543991088867</v>
+        <v>26.09543609619141</v>
       </c>
       <c r="C63" t="n">
         <v>35.04000091552734</v>
@@ -2228,7 +2228,7 @@
         <v>44104</v>
       </c>
       <c r="B64" t="n">
-        <v>22.30474472045898</v>
+        <v>22.30474281311035</v>
       </c>
       <c r="C64" t="n">
         <v>29.95000076293945</v>
@@ -2255,7 +2255,7 @@
         <v>44135</v>
       </c>
       <c r="B65" t="n">
-        <v>22.78137588500977</v>
+        <v>22.78137016296387</v>
       </c>
       <c r="C65" t="n">
         <v>30.59000015258789</v>
@@ -2282,7 +2282,7 @@
         <v>44165</v>
       </c>
       <c r="B66" t="n">
-        <v>24.82502365112305</v>
+        <v>24.82501792907715</v>
       </c>
       <c r="C66" t="n">
         <v>32.93999862670898</v>
@@ -2309,7 +2309,7 @@
         <v>44196</v>
       </c>
       <c r="B67" t="n">
-        <v>26.12128829956055</v>
+        <v>26.12129020690918</v>
       </c>
       <c r="C67" t="n">
         <v>34.65999984741211</v>
@@ -2363,7 +2363,7 @@
         <v>44255</v>
       </c>
       <c r="B69" t="n">
-        <v>27.41755294799805</v>
+        <v>27.41755676269531</v>
       </c>
       <c r="C69" t="n">
         <v>36.38000106811523</v>
@@ -2392,7 +2392,7 @@
         <v>44286</v>
       </c>
       <c r="B70" t="n">
-        <v>30.45407104492188</v>
+        <v>30.45406913757324</v>
       </c>
       <c r="C70" t="n">
         <v>40</v>
@@ -2421,7 +2421,7 @@
         <v>44316</v>
       </c>
       <c r="B71" t="n">
-        <v>31.43619918823242</v>
+        <v>31.43620300292969</v>
       </c>
       <c r="C71" t="n">
         <v>41.29000091552734</v>
@@ -2450,7 +2450,7 @@
         <v>44347</v>
       </c>
       <c r="B72" t="n">
-        <v>33.49053955078125</v>
+        <v>33.49053192138672</v>
       </c>
       <c r="C72" t="n">
         <v>43.59000015258789</v>
@@ -2479,7 +2479,7 @@
         <v>44377</v>
       </c>
       <c r="B73" t="n">
-        <v>31.33158683776855</v>
+        <v>31.33158493041992</v>
       </c>
       <c r="C73" t="n">
         <v>40.77999877929688</v>
@@ -2508,7 +2508,7 @@
         <v>44408</v>
       </c>
       <c r="B74" t="n">
-        <v>29.55679512023926</v>
+        <v>29.55679702758789</v>
       </c>
       <c r="C74" t="n">
         <v>38.47000122070312</v>
@@ -2537,7 +2537,7 @@
         <v>44439</v>
       </c>
       <c r="B75" t="n">
-        <v>27.96104049682617</v>
+        <v>27.9610424041748</v>
       </c>
       <c r="C75" t="n">
         <v>35.9900016784668</v>
@@ -2566,7 +2566,7 @@
         <v>44469</v>
       </c>
       <c r="B76" t="n">
-        <v>28.60587310791016</v>
+        <v>28.60587692260742</v>
       </c>
       <c r="C76" t="n">
         <v>36.81999969482422</v>
@@ -2595,7 +2595,7 @@
         <v>44500</v>
       </c>
       <c r="B77" t="n">
-        <v>27.88335418701172</v>
+        <v>27.88335227966309</v>
       </c>
       <c r="C77" t="n">
         <v>35.88999938964844</v>
@@ -2624,7 +2624,7 @@
         <v>44530</v>
       </c>
       <c r="B78" t="n">
-        <v>26.40687561035156</v>
+        <v>26.4068775177002</v>
       </c>
       <c r="C78" t="n">
         <v>33.61000061035156</v>
@@ -2740,7 +2740,7 @@
         <v>44651</v>
       </c>
       <c r="B82" t="n">
-        <v>31.27580070495605</v>
+        <v>31.27579498291016</v>
       </c>
       <c r="C82" t="n">
         <v>39.38999938964844</v>
@@ -2769,7 +2769,7 @@
         <v>44681</v>
       </c>
       <c r="B83" t="n">
-        <v>33.8483772277832</v>
+        <v>33.84836959838867</v>
       </c>
       <c r="C83" t="n">
         <v>42.63000106811523</v>
@@ -2798,7 +2798,7 @@
         <v>44712</v>
       </c>
       <c r="B84" t="n">
-        <v>30.34148788452148</v>
+        <v>30.34148216247559</v>
       </c>
       <c r="C84" t="n">
         <v>37.83000183105469</v>
@@ -2827,7 +2827,7 @@
         <v>44742</v>
       </c>
       <c r="B85" t="n">
-        <v>30.59011268615723</v>
+        <v>30.59011459350586</v>
       </c>
       <c r="C85" t="n">
         <v>38.13999938964844</v>
@@ -2856,7 +2856,7 @@
         <v>44773</v>
       </c>
       <c r="B86" t="n">
-        <v>29.5394344329834</v>
+        <v>29.5394401550293</v>
       </c>
       <c r="C86" t="n">
         <v>36.83000183105469</v>
@@ -2914,7 +2914,7 @@
         <v>44834</v>
       </c>
       <c r="B88" t="n">
-        <v>27.0261402130127</v>
+        <v>27.02614402770996</v>
       </c>
       <c r="C88" t="n">
         <v>33.34999847412109</v>
@@ -2943,7 +2943,7 @@
         <v>44865</v>
       </c>
       <c r="B89" t="n">
-        <v>31.1752815246582</v>
+        <v>31.17528533935547</v>
       </c>
       <c r="C89" t="n">
         <v>38.47000122070312</v>
@@ -2972,7 +2972,7 @@
         <v>44895</v>
       </c>
       <c r="B90" t="n">
-        <v>32.21920394897461</v>
+        <v>32.21921157836914</v>
       </c>
       <c r="C90" t="n">
         <v>39.34999847412109</v>
@@ -3030,7 +3030,7 @@
         <v>44957</v>
       </c>
       <c r="B92" t="n">
-        <v>33.18537521362305</v>
+        <v>33.18537902832031</v>
       </c>
       <c r="C92" t="n">
         <v>40.52999877929688</v>
@@ -3059,7 +3059,7 @@
         <v>44985</v>
       </c>
       <c r="B93" t="n">
-        <v>31.88349914550781</v>
+        <v>31.88350868225098</v>
       </c>
       <c r="C93" t="n">
         <v>38.93999862670898</v>
@@ -3088,7 +3088,7 @@
         <v>45016</v>
       </c>
       <c r="B94" t="n">
-        <v>31.99642372131348</v>
+        <v>31.99642181396484</v>
       </c>
       <c r="C94" t="n">
         <v>38.66999816894531</v>
@@ -3146,7 +3146,7 @@
         <v>45077</v>
       </c>
       <c r="B96" t="n">
-        <v>31.62408638000488</v>
+        <v>31.62408828735352</v>
       </c>
       <c r="C96" t="n">
         <v>38.22000122070312</v>
@@ -3175,7 +3175,7 @@
         <v>45107</v>
       </c>
       <c r="B97" t="n">
-        <v>29.68179512023926</v>
+        <v>29.68179702758789</v>
       </c>
       <c r="C97" t="n">
         <v>35.5</v>
@@ -3204,7 +3204,7 @@
         <v>45138</v>
       </c>
       <c r="B98" t="n">
-        <v>30.25035667419434</v>
+        <v>30.25035285949707</v>
       </c>
       <c r="C98" t="n">
         <v>36.18000030517578</v>
@@ -3262,7 +3262,7 @@
         <v>45199</v>
       </c>
       <c r="B100" t="n">
-        <v>28.46480178833008</v>
+        <v>28.46480369567871</v>
       </c>
       <c r="C100" t="n">
         <v>33.63999938964844</v>
@@ -3320,7 +3320,7 @@
         <v>45260</v>
       </c>
       <c r="B102" t="n">
-        <v>30.05131721496582</v>
+        <v>30.05131340026855</v>
       </c>
       <c r="C102" t="n">
         <v>35.11000061035156</v>
@@ -3349,7 +3349,7 @@
         <v>45291</v>
       </c>
       <c r="B103" t="n">
-        <v>31.65188789367676</v>
+        <v>31.65188980102539</v>
       </c>
       <c r="C103" t="n">
         <v>36.97999954223633</v>
@@ -3378,7 +3378,7 @@
         <v>45322</v>
       </c>
       <c r="B104" t="n">
-        <v>31.78027534484863</v>
+        <v>31.78027725219727</v>
       </c>
       <c r="C104" t="n">
         <v>37.13000106811523</v>
@@ -3407,7 +3407,7 @@
         <v>45351</v>
       </c>
       <c r="B105" t="n">
-        <v>30.19682312011719</v>
+        <v>30.19682121276855</v>
       </c>
       <c r="C105" t="n">
         <v>35.27999877929688</v>
@@ -3436,7 +3436,7 @@
         <v>45382</v>
       </c>
       <c r="B106" t="n">
-        <v>31.94489097595215</v>
+        <v>31.94488525390625</v>
       </c>
       <c r="C106" t="n">
         <v>36.90000152587891</v>
@@ -3465,7 +3465,7 @@
         <v>45412</v>
       </c>
       <c r="B107" t="n">
-        <v>33.42525482177734</v>
+        <v>33.42525863647461</v>
       </c>
       <c r="C107" t="n">
         <v>38.61000061035156</v>
@@ -3494,7 +3494,7 @@
         <v>45443</v>
       </c>
       <c r="B108" t="n">
-        <v>30.62033843994141</v>
+        <v>30.62034034729004</v>
       </c>
       <c r="C108" t="n">
         <v>35.36999893188477</v>
@@ -3552,7 +3552,7 @@
         <v>45504</v>
       </c>
       <c r="B110" t="n">
-        <v>30.83760833740234</v>
+        <v>30.83760452270508</v>
       </c>
       <c r="C110" t="n">
         <v>35.20999908447266</v>
@@ -3581,7 +3581,7 @@
         <v>45535</v>
       </c>
       <c r="B111" t="n">
-        <v>31.38634872436523</v>
+        <v>31.3863468170166</v>
       </c>
       <c r="C111" t="n">
         <v>35.43000030517578</v>
@@ -3639,7 +3639,7 @@
         <v>45596</v>
       </c>
       <c r="B113" t="n">
-        <v>29.64118385314941</v>
+        <v>29.64118576049805</v>
       </c>
       <c r="C113" t="n">
         <v>33.45999908447266</v>
@@ -3697,7 +3697,7 @@
         <v>45657</v>
       </c>
       <c r="B115" t="n">
-        <v>27.5501766204834</v>
+        <v>27.55017471313477</v>
       </c>
       <c r="C115" t="n">
         <v>30.70999908447266</v>
@@ -3755,7 +3755,7 @@
         <v>45716</v>
       </c>
       <c r="B117" t="n">
-        <v>27.5501766204834</v>
+        <v>27.55017471313477</v>
       </c>
       <c r="C117" t="n">
         <v>30.70999908447266</v>
@@ -3784,7 +3784,7 @@
         <v>45747</v>
       </c>
       <c r="B118" t="n">
-        <v>27.65260124206543</v>
+        <v>27.65259742736816</v>
       </c>
       <c r="C118" t="n">
         <v>30.43000030517578</v>
@@ -3813,7 +3813,7 @@
         <v>45777</v>
       </c>
       <c r="B119" t="n">
-        <v>26.44399070739746</v>
+        <v>26.44399261474609</v>
       </c>
       <c r="C119" t="n">
         <v>29.10000038146973</v>
